--- a/base/StructureDefinition-SGActivityDefinition.xlsx
+++ b/base/StructureDefinition-SGActivityDefinition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="529">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T12:10:23+02:00</t>
+    <t>2026-08-27T08:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>adf-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}
-dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}shr-1:If knowledge capabilities are stated, they SHALL include shareable {extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').exists() implies extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').where(value = 'shareable').exists()}</t>
   </si>
   <si>
     <t>Act[classCode=ACT; moodCode=DEFN]</t>
@@ -358,7 +358,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -459,20 +459,8 @@
     <t>Defines a knowledge capability afforded by this knowledge artifact.</t>
   </si>
   <si>
-    <t>ActivityDefinition.extension:artifactComment</t>
-  </si>
-  <si>
-    <t>artifactComment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {cqf-artifactComment}
+    <t xml:space="preserve">ele-1
 </t>
-  </si>
-  <si>
-    <t>Additional documentation, review, or usage guidance</t>
-  </si>
-  <si>
-    <t>A comment containing additional documentation, a review comment, usage guidance, or other relevant information from a particular user.</t>
   </si>
   <si>
     <t>ActivityDefinition.extension:versionAlgorithm</t>
@@ -508,6 +496,22 @@
   </si>
   <si>
     <t>Defines the versioning policy of the artifact.</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.extension:webSource</t>
+  </si>
+  <si>
+    <t>webSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {web-source}
+</t>
+  </si>
+  <si>
+    <t>web-source</t>
+  </si>
+  <si>
+    <t>Where a human readable web page describing the resource can be found, if it's at a different location to the canonical URL itself.</t>
   </si>
   <si>
     <t>ActivityDefinition.modifierExtension</t>
@@ -714,7 +718,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Group)</t>
+Reference(Group|4.0.1)</t>
   </si>
   <si>
     <t>Type of individual the activity definition is intended for</t>
@@ -732,7 +736,7 @@
     <t>The possible types of subjects for an activity (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subject-type</t>
+    <t>http://hl7.org/fhir/ValueSet/subject-type|4.0.1</t>
   </si>
   <si>
     <t>Definition.subject</t>
@@ -876,7 +880,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -1014,7 +1018,7 @@
     <t>High-level categorization of the definition, used for searching, sorting, and filtering.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/definition-topic</t>
+    <t>http://hl7.org/fhir/ValueSet/definition-topic|4.0.1</t>
   </si>
   <si>
     <t>ActivityDefinition.author</t>
@@ -1084,7 +1088,7 @@
     <t>ActivityDefinition.library</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(Library)
+    <t xml:space="preserve">canonical(Library|4.0.1)
 </t>
   </si>
   <si>
@@ -1121,7 +1125,7 @@
     <t>ActivityDefinition.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1152,7 +1156,7 @@
     <t>Detailed type of the activity; e.g. CBC.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
   </si>
   <si>
     <t>.code</t>
@@ -1226,7 +1230,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1335,7 +1339,7 @@
     <t>Defines roles played by participants for the action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/action-participant-role|4.0.1</t>
   </si>
   <si>
     <t>.role.code</t>
@@ -1344,7 +1348,7 @@
     <t>ActivityDefinition.product[x]</t>
   </si>
   <si>
-    <t>Reference(Medication|Substance)
+    <t>Reference(Medication|4.0.1|Substance|4.0.1)
 CodeableConcept</t>
   </si>
   <si>
@@ -1357,7 +1361,7 @@
     <t>Code describing the type of substance or medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -1392,10 +1396,10 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>ActivityDefinition.product[x]:productReference.extension:artifactReference</t>
-  </si>
-  <si>
-    <t>artifactReference</t>
+    <t>ActivityDefinition.product[x]:productReference.extension:nonCanonicalReference</t>
+  </si>
+  <si>
+    <t>nonCanonicalReference</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {artifact-uriReference}
@@ -1449,7 +1453,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1501,7 +1505,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1551,7 +1555,7 @@
     <t>A code that identifies the anatomical location.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>.targetSiteCode {for classCode=PROC, SBADM}</t>
@@ -1560,7 +1564,7 @@
     <t>ActivityDefinition.specimenRequirement</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(SpecimenDefinition)
+    <t xml:space="preserve">Reference(SpecimenDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1576,7 +1580,7 @@
     <t>ActivityDefinition.observationRequirement</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ObservationDefinition)
+    <t xml:space="preserve">Reference(ObservationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1601,7 +1605,7 @@
     <t>ActivityDefinition.transform</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureMap)
+    <t xml:space="preserve">canonical(StructureMap|4.0.1)
 </t>
   </si>
   <si>
@@ -1980,17 +1984,17 @@
   <dimension ref="A1:AN78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="68.63671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.58984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.65234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="65.18359375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.81640625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.5859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="34.17578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="36.54296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1999,26 +2003,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="90.05859375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.30859375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="80.078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.359375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.34765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="53.828125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="129.28125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="43.078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="48.2890625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="114.75" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3047,7 +3051,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>137</v>
       </c>
@@ -3143,7 +3147,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>136</v>
@@ -3161,15 +3165,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
@@ -3179,7 +3183,7 @@
         <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>86</v>
@@ -3191,15 +3195,17 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3257,7 +3263,7 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>136</v>
@@ -3277,13 +3283,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
@@ -3296,7 +3302,7 @@
         <v>85</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -3305,17 +3311,15 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3373,7 +3377,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>136</v>
@@ -3391,15 +3395,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
@@ -3421,13 +3425,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3487,7 +3491,7 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>136</v>
@@ -3507,14 +3511,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3536,16 +3540,16 @@
         <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3594,7 +3598,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3621,12 +3625,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3652,16 +3656,16 @@
         <v>99</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3710,7 +3714,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3725,13 +3729,13 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
@@ -3739,10 +3743,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3765,19 +3769,19 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3826,7 +3830,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3841,24 +3845,24 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3881,16 +3885,16 @@
         <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3940,7 +3944,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3955,24 +3959,24 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3995,19 +3999,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -4056,7 +4060,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -4065,7 +4069,7 @@
         <v>85</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>97</v>
@@ -4083,12 +4087,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4111,16 +4115,16 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4170,7 +4174,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -4185,10 +4189,10 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -4199,10 +4203,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4225,13 +4229,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4282,7 +4286,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4309,12 +4313,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4340,13 +4344,13 @@
         <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4372,13 +4376,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4396,7 +4400,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>85</v>
@@ -4411,24 +4415,24 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4451,19 +4455,19 @@
         <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4512,7 +4516,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4527,13 +4531,13 @@
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
@@ -4541,10 +4545,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4567,13 +4571,13 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4581,7 +4585,7 @@
         <v>20</v>
       </c>
       <c r="Q23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R23" t="s" s="2">
         <v>20</v>
@@ -4602,13 +4606,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4626,7 +4630,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4641,7 +4645,7 @@
         <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
@@ -4655,14 +4659,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4681,16 +4685,16 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4740,7 +4744,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4755,24 +4759,24 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4795,19 +4799,19 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4856,7 +4860,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4871,13 +4875,13 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
@@ -4885,10 +4889,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4911,16 +4915,16 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4970,7 +4974,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4985,10 +4989,10 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
@@ -4997,12 +5001,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5025,16 +5029,16 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5084,7 +5088,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -5099,10 +5103,10 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
@@ -5113,10 +5117,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5139,19 +5143,19 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5200,7 +5204,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -5215,10 +5219,10 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
@@ -5229,10 +5233,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5255,16 +5259,16 @@
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5290,13 +5294,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5314,7 +5318,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5329,10 +5333,10 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
@@ -5343,10 +5347,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5369,16 +5373,16 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5428,7 +5432,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5443,24 +5447,24 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5483,13 +5487,13 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5540,7 +5544,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5558,7 +5562,7 @@
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>20</v>
@@ -5569,14 +5573,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5595,17 +5599,17 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5654,7 +5658,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5669,24 +5673,24 @@
         <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5709,16 +5713,16 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5768,7 +5772,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5783,24 +5787,24 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5823,19 +5827,19 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5884,7 +5888,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5899,24 +5903,24 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5939,19 +5943,19 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6000,7 +6004,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -6015,24 +6019,24 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6055,17 +6059,17 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6090,13 +6094,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6114,7 +6118,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6132,7 +6136,7 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
@@ -6143,10 +6147,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6169,13 +6173,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6226,7 +6230,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6244,7 +6248,7 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>20</v>
@@ -6255,10 +6259,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6281,13 +6285,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6338,7 +6342,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6367,10 +6371,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6393,13 +6397,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6450,7 +6454,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6468,7 +6472,7 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
@@ -6479,10 +6483,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6505,13 +6509,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6562,7 +6566,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6580,7 +6584,7 @@
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>20</v>
@@ -6591,10 +6595,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6617,19 +6621,19 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6678,7 +6682,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6696,7 +6700,7 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>20</v>
@@ -6707,10 +6711,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6733,13 +6737,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6790,7 +6794,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6808,7 +6812,7 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>20</v>
@@ -6819,10 +6823,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6848,13 +6852,13 @@
         <v>105</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6880,13 +6884,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6904,7 +6908,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6922,7 +6926,7 @@
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
@@ -6933,10 +6937,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6959,17 +6963,17 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7018,7 +7022,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -7047,10 +7051,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7073,19 +7077,19 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7110,13 +7114,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -7134,7 +7138,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7152,7 +7156,7 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>20</v>
@@ -7163,10 +7167,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7192,10 +7196,10 @@
         <v>105</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7222,13 +7226,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7246,7 +7250,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7275,10 +7279,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7304,10 +7308,10 @@
         <v>105</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7334,13 +7338,13 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7358,7 +7362,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7387,10 +7391,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7413,16 +7417,16 @@
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7472,7 +7476,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7501,10 +7505,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7527,17 +7531,17 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7586,7 +7590,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7604,7 +7608,7 @@
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>20</v>
@@ -7615,14 +7619,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7641,19 +7645,19 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7702,7 +7706,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7720,7 +7724,7 @@
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>20</v>
@@ -7731,10 +7735,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7757,13 +7761,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7814,7 +7818,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7832,7 +7836,7 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>20</v>
@@ -7843,10 +7847,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7869,13 +7873,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7926,7 +7930,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7944,7 +7948,7 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>20</v>
@@ -7955,14 +7959,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7984,13 +7988,13 @@
         <v>130</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8040,7 +8044,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8058,7 +8062,7 @@
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
@@ -8069,14 +8073,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8098,16 +8102,16 @@
         <v>130</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8156,7 +8160,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8185,10 +8189,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8214,10 +8218,10 @@
         <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8244,13 +8248,13 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -8268,7 +8272,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>85</v>
@@ -8286,7 +8290,7 @@
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>20</v>
@@ -8297,10 +8301,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8323,13 +8327,13 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8356,13 +8360,13 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -8380,7 +8384,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8398,7 +8402,7 @@
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>20</v>
@@ -8409,10 +8413,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8435,13 +8439,13 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8468,19 +8472,19 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
@@ -8490,7 +8494,7 @@
         <v>134</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8508,7 +8512,7 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>20</v>
@@ -8517,15 +8521,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>20</v>
@@ -8538,7 +8542,7 @@
         <v>85</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>20</v>
@@ -8547,13 +8551,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8604,7 +8608,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8622,7 +8626,7 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>20</v>
@@ -8633,10 +8637,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8659,13 +8663,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8716,7 +8720,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8734,7 +8738,7 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>20</v>
@@ -8745,14 +8749,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8774,13 +8778,13 @@
         <v>130</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8821,7 +8825,7 @@
         <v>133</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>20</v>
@@ -8830,7 +8834,7 @@
         <v>134</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8848,7 +8852,7 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>20</v>
@@ -8857,15 +8861,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>20</v>
@@ -8887,13 +8891,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8944,7 +8948,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8973,10 +8977,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8999,16 +9003,16 @@
         <v>86</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9058,7 +9062,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -9067,7 +9071,7 @@
         <v>85</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>97</v>
@@ -9087,10 +9091,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9116,13 +9120,13 @@
         <v>99</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9148,13 +9152,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -9172,7 +9176,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9201,10 +9205,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9227,16 +9231,16 @@
         <v>86</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9286,7 +9290,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9304,7 +9308,7 @@
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>20</v>
@@ -9315,10 +9319,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9341,16 +9345,16 @@
         <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9400,7 +9404,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9429,14 +9433,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9455,13 +9459,13 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9512,7 +9516,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9530,7 +9534,7 @@
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>20</v>
@@ -9541,10 +9545,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9567,16 +9571,16 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9626,7 +9630,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9644,7 +9648,7 @@
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>20</v>
@@ -9655,10 +9659,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9681,19 +9685,19 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -9718,13 +9722,13 @@
         <v>20</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>20</v>
@@ -9742,7 +9746,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9760,7 +9764,7 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>20</v>
@@ -9771,10 +9775,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9797,17 +9801,17 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -9856,7 +9860,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9885,10 +9889,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9911,17 +9915,17 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -9970,7 +9974,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9999,10 +10003,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10025,13 +10029,13 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10082,7 +10086,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10111,10 +10115,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10137,16 +10141,16 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10196,7 +10200,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10225,10 +10229,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10251,16 +10255,16 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10310,7 +10314,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10339,10 +10343,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10365,13 +10369,13 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10422,7 +10426,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10440,7 +10444,7 @@
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>20</v>
@@ -10451,14 +10455,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10480,13 +10484,13 @@
         <v>130</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10536,7 +10540,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10554,7 +10558,7 @@
         <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>20</v>
@@ -10565,14 +10569,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10594,16 +10598,16 @@
         <v>130</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -10652,7 +10656,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10681,10 +10685,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10707,16 +10711,16 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10766,7 +10770,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>85</v>
@@ -10795,10 +10799,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10821,16 +10825,16 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10880,7 +10884,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>85</v>
@@ -10909,12 +10913,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN78">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
